--- a/docs/deliverables/out/Programme/Common/BIBS_Glossary_BRD-00_Programme_Glossary_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Common/BIBS_Glossary_BRD-00_Programme_Glossary_v1.0.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Glossary'!$A$4:$C$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Glossary'!$A$4:$C$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Glossary'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
@@ -926,7 +926,7 @@
       <c r="C7" s="12" t="inlineStr"/>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Control, Data, Document, Environment, Integration, Method, Organisation, Quality, System, User Access</t>
+          <t>Control, Data, Document, Environment, Integration, Method, Organisation, Quality, Scope, System, User Access</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1628,131 +1628,131 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>PHT</t>
+          <t>Phase 2</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Philippine time (UTC+8).</t>
+          <t>Functions the client deferred beyond the current phase (decisions of 17-Oct-2026): reinsurance and the partner portal of Employee Benefits. Kept as a baseline, hidden from the BDOI roles and not counted in the current-phase conformance figures.</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Reconciliation</t>
+          <t>PHT</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Daily comparison of the users and group profiles of BIBS with UIDM-ISC.</t>
+          <t>Philippine time (UTC+8).</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>User Access</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>RNO</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Reports, Notifications and Outputs of a BRD.</t>
+          <t>Daily comparison of the users and group profiles of BIBS with UIDM-ISC.</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>User Access</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>RPO, RTO</t>
+          <t>RNO</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Recovery point and recovery time objectives.</t>
+          <t>Reports, Notifications and Outputs of a BRD.</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>RTM</t>
+          <t>RPO, RTO</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Requirements traceability matrix and test cases: BRD, requirement, user story, screen, test case.</t>
+          <t>Recovery point and recovery time objectives.</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Quality</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>SCIM 2.0</t>
+          <t>RTM</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Standard for provisioning users and group membership, used by UIDM-ISC.</t>
+          <t>Requirements traceability matrix and test cases: BRD, requirement, user story, screen, test case.</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Document</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Second approval</t>
+          <t>SCIM 2.0</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Approval by a second checker of a privileged or out-of-hours change.</t>
+          <t>Standard for provisioning users and group membership, used by UIDM-ISC.</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Integration</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Separation of duties (SoD)</t>
+          <t>Second approval</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Rule that two group profiles or permissions are not held by one user.</t>
+          <t>Approval by a second checker of a privileged or out-of-hours change.</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -1764,97 +1764,97 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Story points</t>
+          <t>Separation of duties (SoD)</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Relative size of a user story (first estimate).</t>
+          <t>Rule that two group profiles or permissions are not held by one user.</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Control</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Test account</t>
+          <t>Story points</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>Local account for testing in DEV, SIT and UAT only; never in production.</t>
+          <t>Relative size of a user story (first estimate).</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>User Access</t>
+          <t>Method</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>UIDM-ISC</t>
+          <t>Test account</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>BDOI identity governance platform; source of users and group-profile membership.</t>
+          <t>Local account for testing in DEV, SIT and UAT only; never in production.</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>User Access</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>User story</t>
+          <t>UIDM-ISC</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>Need of a persona: As a ..., I want ..., so that ....</t>
+          <t>BDOI identity governance platform; source of users and group-profile membership.</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>System</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>USR</t>
+          <t>User story</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>User Stories workbook of a BRD.</t>
+          <t>Need of a persona: As a ..., I want ..., so that ....</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>Document</t>
+          <t>Method</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>UXD</t>
+          <t>USR</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>UX Design Specification: every screen of a BRD with a screenshot per page.</t>
+          <t>User Stories workbook of a BRD.</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -1866,33 +1866,50 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
+          <t>UXD</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>UX Design Specification: every screen of a BRD with a screenshot per page.</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
           <t>WCAG 2.2 AA</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Web accessibility guidelines level AA (NFR-ACC-01).</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C56"/>
+  <autoFilter ref="A4:C57"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:C556">
+  <conditionalFormatting sqref="A5:C557">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C556" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Area" error="Choose a value from the list (Area)." type="list">
-      <formula1>'Lists'!$A$2:$A$11</formula1>
+    <dataValidation sqref="C5:C557" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Area" error="Choose a value from the list (Area)." type="list">
+      <formula1>'Lists'!$A$2:$A$12</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -1915,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1987,12 +2004,19 @@
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>User Access</t>
         </is>
